--- a/temp_mhr/asignar_plan_53077367.xlsx
+++ b/temp_mhr/asignar_plan_53077367.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>53072050</t>
+          <t>53074230</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -470,7 +470,330 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>700141999</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>501122514</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>700174923</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>501154088</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>700175804</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>501154979</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>700177422</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>501156327</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>700178919</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>501157784</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>700179711</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>501158586</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>700176879</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>501155764</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>700176876</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>501155761</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>700171486</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>501150591</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>700179809</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>501158684</t>
         </is>
       </c>
     </row>

--- a/temp_mhr/asignar_plan_53077367.xlsx
+++ b/temp_mhr/asignar_plan_53077367.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -470,14 +470,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>700141999</t>
+          <t>700178427</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -487,14 +487,14 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>501122514</t>
+          <t>501157292</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -504,14 +504,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>700174923</t>
+          <t>700177419</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -521,14 +521,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>501154088</t>
+          <t>501156324</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -538,14 +538,14 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>700175804</t>
+          <t>700173276</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -555,14 +555,14 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>501154979</t>
+          <t>501152401</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -572,14 +572,14 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>700177422</t>
+          <t>700176004</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -589,14 +589,14 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>501156327</t>
+          <t>501155179</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -606,14 +606,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>700178919</t>
+          <t>700172712</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -623,14 +623,14 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>501157784</t>
+          <t>501151817</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -640,14 +640,14 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>700179711</t>
+          <t>700177862</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>501158586</t>
+          <t>501156767</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>700176879</t>
+          <t>700179970</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -691,14 +691,14 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>501155764</t>
+          <t>501158845</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>700176876</t>
+          <t>700179267</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -725,14 +725,14 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>501155761</t>
+          <t>501158132</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>700171486</t>
+          <t>700179242</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -759,14 +759,14 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>501150591</t>
+          <t>501158107</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>700179809</t>
+          <t>700173778</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53072050</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -793,7 +793,5617 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>501152909</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>700176953</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>501155848</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>700177601</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>501156508</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>700180683</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>501159568</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>700172703</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>501151808</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>700169644</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>501148699</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>700171901</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>501150996</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>700166215</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>501145220</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>700172033</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>501151138</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>700176646</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>501155524</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>700177420</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>501156325</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>700177715</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>501156620</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>700178920</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>501157785</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>700177863</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>501156768</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>700165550</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>501144545</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>700178059</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>501156924</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>700179809</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
           <t>501158684</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>700179241</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>501158106</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>700177991</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>501156846</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>700176879</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>501155764</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>700176952</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>501155847</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>700179027</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>501157892</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>700177422</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>501156327</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>700175991</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>501155166</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>700178454</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>501157320</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>700171902</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>501150997</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>700177238</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>501156133</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>700053347</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>501072229</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>700180685</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>501159570</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>700176647</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>501155525</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>700178882</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>501157747</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>700177984</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>501156839</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>700176961</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>501155856</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>700179002</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>501157877</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>700067969</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>501069891</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>700177066</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>501155964</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>700177861</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>501156766</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>700177714</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>501156619</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>700178879</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>501157744</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>700167435</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>501146450</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>700057757</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>501030118</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>700176645</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>501155523</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>700178838</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>501157703</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>700177864</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>501156769</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>700176979</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>501155874</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>700177239</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>501156134</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>700179001</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>501157876</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>700178205</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>501157070</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>700176956</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>501155851</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>700177922</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>501156827</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>700177580</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>501156485</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>700178417</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>501157282</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>700176876</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>501155761</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>700141999</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>501122514</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>700180684</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>501159569</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>700178419</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>501157284</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>700172682</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>501151787</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>700176935</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>501155830</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>700165551</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>501144546</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>700179520</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>501158385</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>700175796</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>501154961</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>700174925</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>501154090</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>700173780</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>501152910</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>700178893</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>501157758</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>700041189</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>501040417</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>700173880</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>501153015</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>700177989</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>501156844</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>700171933</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>501151038</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>700178598</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>501157465</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>700178878</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>501157743</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>700177592</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>501156499</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>700175804</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>501154979</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>700179240</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>501158105</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>700176881</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>501155766</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>700169941</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>501148996</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>700179371</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>501158236</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>700176949</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>501155844</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>700177421</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>501156326</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>700171934</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>501151039</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>700177713</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>501156618</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>700057758</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>501030119</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>700176644</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>501155522</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>700179519</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>501158384</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>700172710</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>501151815</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>700177866</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>501156771</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>700177581</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>501156486</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>700178186</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>501157051</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>700177988</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>501156843</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>700176950</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>501155845</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>700179711</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>501158586</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>700178206</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>501157071</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>700177067</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>501155965</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>700176978</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>501155873</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>700178455</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>501157321</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>700178918</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>501157783</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>700172711</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>501151816</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>700179368</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>501158233</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>700178919</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>501157784</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>700178880</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>501157745</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>700178418</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>501157283</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>700179239</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>501158104</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>700176955</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>501155850</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>700177716</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>501156621</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>700176962</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>501155857</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>700041190</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>501040418</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>700177630</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>501156535</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>700179521</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>501158386</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>700175797</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>501154962</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>700172034</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>501151139</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>700178837</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>501157702</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>700178597</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>501157464</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>700174926</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>501154091</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>700178420</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>501157285</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>700177717</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>501156622</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>700177603</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>501156518</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>700178187</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>501157052</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>700179026</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>501157891</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>700176976</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>501155871</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>700177985</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>501156840</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>700177582</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>501156487</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>700177865</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>501156770</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>700180612</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>501159507</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>700174924</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>501154089</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>700175990</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>501155165</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>700172266</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>501151371</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>700176877</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>501155762</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>700178881</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>501157746</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>700176878</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>501155763</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>700173879</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>501153014</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>700169940</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>501148995</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>700177602</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>501156509</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>700177631</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>501156536</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>700179266</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>501158131</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>700179369</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>501158234</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>700177835</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>501156750</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>700177065</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>501155963</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>700176003</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>501155178</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>700178422</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>501157287</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>700177692</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>501156597</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>700177983</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>501156838</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>700172265</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>501151370</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>700178921</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>501157786</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>700177240</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>501156135</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>700165552</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>501144547</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>700176880</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>501155765</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>700177441</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>501156346</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>700180464</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>501159359</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>700179370</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>501158235</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>700174923</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>501154088</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>700175824</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>501154999</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>700166216</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>501145221</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>700178421</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>501157286</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>700178058</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>501156923</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>700176936</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>501155831</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>700177068</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>501155966</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>700177594</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>501156501</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>700177836</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>501156751</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>700175805</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>501154980</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>700176977</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>501155872</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>700165563</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>501144558</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>700172709</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>501151814</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>700179522</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>501158387</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>700176152</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>501155327</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>700178426</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>501157291</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>700142000</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>501122515</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>700175823</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>53072050</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>501154998</t>
         </is>
       </c>
     </row>
